--- a/artfynd/A 22154-2026 artfynd.xlsx
+++ b/artfynd/A 22154-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131033306</v>
+        <v>131033360</v>
       </c>
       <c r="B2" t="n">
-        <v>79007</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396036</v>
+        <v>395791</v>
       </c>
       <c r="R2" t="n">
-        <v>6804797</v>
+        <v>6804722</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131033337</v>
+        <v>131033361</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>395826</v>
+        <v>395806</v>
       </c>
       <c r="R3" t="n">
-        <v>6804765</v>
+        <v>6804660</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131033355</v>
+        <v>131033307</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>396033</v>
+        <v>395820</v>
       </c>
       <c r="R4" t="n">
-        <v>6804799</v>
+        <v>6804634</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131033363</v>
+        <v>131033318</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>395670</v>
+        <v>395666</v>
       </c>
       <c r="R5" t="n">
-        <v>6804622</v>
+        <v>6804680</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131033339</v>
+        <v>131033319</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>395811</v>
+        <v>395654</v>
       </c>
       <c r="R6" t="n">
-        <v>6804663</v>
+        <v>6804639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,50 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131033290</v>
+        <v>131033320</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>395641</v>
+        <v>395688</v>
       </c>
       <c r="R7" t="n">
-        <v>6804799</v>
+        <v>6804619</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,12 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131033281</v>
+        <v>131033321</v>
       </c>
       <c r="B8" t="n">
-        <v>79868</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>395662</v>
+        <v>395718</v>
       </c>
       <c r="R8" t="n">
-        <v>6804783</v>
+        <v>6804573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131033360</v>
+        <v>131033335</v>
       </c>
       <c r="B9" t="n">
-        <v>78915</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>395791</v>
+        <v>395768</v>
       </c>
       <c r="R9" t="n">
-        <v>6804722</v>
+        <v>6804642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,14 +1531,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131033338</v>
+        <v>131033336</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1576,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>395824</v>
+        <v>395777</v>
       </c>
       <c r="R10" t="n">
-        <v>6804713</v>
+        <v>6804741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131033361</v>
+        <v>131033337</v>
       </c>
       <c r="B11" t="n">
-        <v>78915</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>395806</v>
+        <v>395826</v>
       </c>
       <c r="R11" t="n">
-        <v>6804660</v>
+        <v>6804765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131033340</v>
+        <v>131033338</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1790,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>395817</v>
+        <v>395824</v>
       </c>
       <c r="R12" t="n">
-        <v>6804597</v>
+        <v>6804713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,14 +1852,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131033319</v>
+        <v>131033339</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1897,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395654</v>
+        <v>395811</v>
       </c>
       <c r="R13" t="n">
-        <v>6804639</v>
+        <v>6804663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,14 +1959,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131033320</v>
+        <v>131033340</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2004,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>395688</v>
+        <v>395817</v>
       </c>
       <c r="R14" t="n">
-        <v>6804619</v>
+        <v>6804597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,50 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131033358</v>
+        <v>131033341</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>395749</v>
+        <v>395797</v>
       </c>
       <c r="R15" t="n">
-        <v>6804605</v>
+        <v>6804591</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,19 +2146,14 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Troliga färska spår efter födosökande tretåig hackspett</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2193,54 +2173,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131033301</v>
+        <v>131033355</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>395819</v>
+        <v>396033</v>
       </c>
       <c r="R16" t="n">
-        <v>6804745</v>
+        <v>6804799</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2282,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,7 +2262,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2310,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131033336</v>
+        <v>131033363</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>395777</v>
+        <v>395670</v>
       </c>
       <c r="R17" t="n">
-        <v>6804741</v>
+        <v>6804622</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131033335</v>
+        <v>131033281</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>395768</v>
+        <v>395662</v>
       </c>
       <c r="R18" t="n">
-        <v>6804642</v>
+        <v>6804783</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131033318</v>
+        <v>131033290</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,34 +2505,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Älgforsen, norr om, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>395666</v>
+        <v>395641</v>
       </c>
       <c r="R19" t="n">
-        <v>6804680</v>
+        <v>6804799</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2579,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,6 +2608,571 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131033295</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>395744</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6804575</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131033358</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>395749</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6804605</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Troliga färska spår efter födosökande tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131033301</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>395819</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6804745</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131033306</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>396036</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6804797</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131033284</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Älgforsen, norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>395828</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6804766</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
